--- a/saafah_dashboard_vercel_data.xlsx
+++ b/saafah_dashboard_vercel_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A14240B-42DB-44DB-917D-F7BA5474A8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C0D779-D61A-4E90-8995-62566644F8B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="960" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="960" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,6 @@
     <sheet name="Sales_Stage_Details" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="365">
   <si>
     <t>SAAFAH Dashboard Google Sheets Template</t>
   </si>
@@ -1149,7 +1148,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#,##0;[Red]\(#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -1397,6 +1396,19 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="12" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1406,19 +1418,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="12" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1924,10 +1923,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:I23">
   <tableColumns count="9">
@@ -2114,24 +2109,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2169,12 +2164,12 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
@@ -4299,7 +4294,7 @@
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="14" style="35" customWidth="1"/>
+    <col min="5" max="5" width="14" style="31" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="52" customWidth="1"/>
   </cols>
@@ -4327,7 +4322,7 @@
       <c r="D4" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="32" t="s">
         <v>252</v>
       </c>
       <c r="F4" s="30" t="s">
@@ -4350,7 +4345,7 @@
       <c r="D5" t="s">
         <v>353</v>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="31">
         <v>330000</v>
       </c>
       <c r="F5" t="s">
@@ -4367,10 +4362,10 @@
       <c r="B6" t="s">
         <v>352</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="35" t="s">
         <v>363</v>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="31">
         <v>1000000</v>
       </c>
       <c r="F6" t="s">
@@ -4387,13 +4382,13 @@
       <c r="B7" t="s">
         <v>357</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="34" t="s">
         <v>362</v>
       </c>
       <c r="D7" t="s">
         <v>354</v>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="31">
         <v>2700000</v>
       </c>
       <c r="F7" t="s">
@@ -4410,13 +4405,13 @@
       <c r="B8" t="s">
         <v>357</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="35" t="s">
         <v>364</v>
       </c>
       <c r="D8" t="s">
         <v>353</v>
       </c>
-      <c r="E8" s="37">
+      <c r="E8" s="33">
         <v>2000000</v>
       </c>
       <c r="F8" t="s">
@@ -4439,7 +4434,7 @@
       <c r="D9" t="s">
         <v>354</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="31" t="s">
         <v>354</v>
       </c>
       <c r="F9" t="s">
@@ -4462,7 +4457,7 @@
       <c r="D10" t="s">
         <v>354</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="31" t="s">
         <v>354</v>
       </c>
       <c r="F10" t="s">
@@ -4491,14 +4486,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -5918,32 +5913,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -6020,14 +6015,14 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -7189,32 +7184,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -7291,14 +7286,14 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -8542,32 +8537,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="32"/>
+      <c r="B3" s="37"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -8586,10 +8581,10 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="32"/>
+      <c r="B7" s="37"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -8655,11 +8650,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
@@ -8695,10 +8690,10 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="39" t="s">
         <v>182</v>
       </c>
-      <c r="B17" s="32"/>
+      <c r="B17" s="37"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
@@ -8750,10 +8745,10 @@
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="39" t="s">
         <v>195</v>
       </c>
-      <c r="B25" s="32"/>
+      <c r="B25" s="37"/>
     </row>
     <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
@@ -9795,35 +9790,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="36" t="s">
         <v>205</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -9872,13 +9867,13 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="39" t="s">
         <v>213</v>
       </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -10230,14 +10225,14 @@
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="39" t="s">
         <v>245</v>
       </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
@@ -11335,28 +11330,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>247</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="36" t="s">
         <v>248</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -12976,24 +12971,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>298</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="36" t="s">
         <v>299</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -14126,39 +14121,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="36" t="s">
         <v>316</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="39" t="s">
         <v>317</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -14212,8 +14207,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="21">
-        <f>COUNTIF(Sales_Raw_Opportunities!F:F,G5)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>326</v>
@@ -14245,8 +14239,7 @@
         <v>0.3</v>
       </c>
       <c r="H6" s="21">
-        <f>COUNTIF(Sales_Raw_Opportunities!F:F,G6)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>326</v>
@@ -14278,8 +14271,7 @@
         <v>0.4</v>
       </c>
       <c r="H7" s="21">
-        <f>COUNTIF(Sales_Raw_Opportunities!F:F,G7)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>326</v>
@@ -14298,34 +14290,32 @@
         <v>50000</v>
       </c>
       <c r="D8" s="13">
-        <f>COUNTIFS(Sales_Raw_Opportunities!H:H,"Won",Sales_Raw_Opportunities!D:D,"Apr 2026")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="24" t="s">
         <v>330</v>
       </c>
       <c r="F8" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="25">
         <v>0.5</v>
       </c>
       <c r="H8" s="21">
-        <f>COUNTIF(Sales_Raw_Opportunities!F:F,G8)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
       <c r="G9" s="26"/>
       <c r="H9" s="21"/>
       <c r="I9" s="2" t="s">
@@ -14451,17 +14441,17 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="39" t="s">
         <v>338</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="39" t="s">
         <v>339</v>
       </c>
-      <c r="B16" s="32"/>
+      <c r="B16" s="37"/>
       <c r="G16" s="18" t="s">
         <v>340</v>
       </c>
